--- a/Plannings 2026 S41.xlsx
+++ b/Plannings 2026 S41.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67222E19-38C5-4D1B-8A2C-A6B62757C2D3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="120">
   <si>
     <t>Planning des salariés du 05/10/2026 au 11/10/2026</t>
   </si>
@@ -372,9 +372,6 @@
     <t>17:30/22:30</t>
   </si>
   <si>
-    <t>INVENTAIRE // C. PADEL // EVENT SAFRAN PU</t>
-  </si>
-  <si>
     <t>C. PADEL // EDF</t>
   </si>
   <si>
@@ -382,6 +379,9 @@
   </si>
   <si>
     <t>C. PADEL // EDF // LEAGUES</t>
+  </si>
+  <si>
+    <t>C. PADEL // EVENT GTM</t>
   </si>
 </sst>
 </file>
@@ -5406,24 +5406,26 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="D3" s="36" t="s">
+      <c r="F3" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="G3" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="F3" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="G3" s="36" t="s">
+      <c r="H3" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="36"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
@@ -7500,13 +7502,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A24D7A2B-9FD9-411E-9456-3A78290D458E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D416C393-5E79-4870-A27A-DCA7B0769528}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFCF5860-6BE1-4684-838A-E84D137BACE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3D62615-20CC-41D7-9549-DFC38910738C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{880A5CE2-4B9F-4A75-A43E-CA6BA6DAC4DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B057C25-B0AE-4E3E-88D5-B45C14832292}"/>
 </file>
--- a/Plannings 2026 S41.xlsx
+++ b/Plannings 2026 S41.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67222E19-38C5-4D1B-8A2C-A6B62757C2D3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="120">
   <si>
     <t>Planning des salariés du 05/10/2026 au 11/10/2026</t>
   </si>
@@ -372,6 +372,9 @@
     <t>17:30/22:30</t>
   </si>
   <si>
+    <t>INVENTAIRE // C. PADEL // EVENT SAFRAN PU</t>
+  </si>
+  <si>
     <t>C. PADEL // EDF</t>
   </si>
   <si>
@@ -379,9 +382,6 @@
   </si>
   <si>
     <t>C. PADEL // EDF // LEAGUES</t>
-  </si>
-  <si>
-    <t>C. PADEL // EVENT GTM</t>
   </si>
 </sst>
 </file>
@@ -5406,26 +5406,24 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>116</v>
-      </c>
       <c r="G3" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" s="36" t="s">
         <v>13</v>
       </c>
+      <c r="H3" s="36"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
@@ -7502,13 +7500,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D416C393-5E79-4870-A27A-DCA7B0769528}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A24D7A2B-9FD9-411E-9456-3A78290D458E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3D62615-20CC-41D7-9549-DFC38910738C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFCF5860-6BE1-4684-838A-E84D137BACE4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B057C25-B0AE-4E3E-88D5-B45C14832292}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{880A5CE2-4B9F-4A75-A43E-CA6BA6DAC4DB}"/>
 </file>
--- a/Plannings 2026 S41.xlsx
+++ b/Plannings 2026 S41.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67222E19-38C5-4D1B-8A2C-A6B62757C2D3}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E19D15AB-0DF8-4E8A-BDAD-034AB4BB581B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,25 @@
     <sheet name="Résultats par salarié" sheetId="2" r:id="rId2"/>
     <sheet name="Informations" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="121">
   <si>
     <t>Planning des salariés du 05/10/2026 au 11/10/2026</t>
   </si>
@@ -382,6 +395,9 @@
   </si>
   <si>
     <t>C. PADEL // EVENT GTM</t>
+  </si>
+  <si>
+    <t>09:15/11:45</t>
   </si>
 </sst>
 </file>
@@ -5004,6 +5020,270 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88A9096C-EADB-49D9-9206-738C26AE5526}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9593036" y="3320143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DF5EF4D-F807-49C4-BDF3-61346F63760B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9593036" y="3701143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ED023F5-B683-4F6E-A1C9-B3C71481A54E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9593036" y="3320143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DC813F5-E885-4555-ABEE-3050D5FDAD78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9593036" y="3701143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EA533BF-E445-4206-9189-410A855FD5CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15988393" y="3320143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ADF761F-DA3C-4D01-9EA0-B1E0B76560BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15988393" y="3320143"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5663,8 +5943,8 @@
       <c r="C18" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>12</v>
+      <c r="D18" s="42" t="s">
+        <v>35</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="42" t="s">
@@ -5681,8 +5961,8 @@
       <c r="C19" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>37</v>
+      <c r="D19" s="43" t="s">
+        <v>120</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="43" t="s">
@@ -5697,8 +5977,8 @@
       <c r="C20" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="40" t="s">
-        <v>35</v>
+      <c r="D20" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="40" t="s">
@@ -5713,8 +5993,8 @@
       <c r="C21" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="39" t="s">
-        <v>16</v>
+      <c r="D21" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="39" t="s">
@@ -5729,7 +6009,9 @@
       <c r="C22" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="39"/>
+      <c r="D22" s="40" t="s">
+        <v>35</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="40" t="s">
         <v>35</v>
@@ -5743,7 +6025,9 @@
       <c r="C23" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="39"/>
+      <c r="D23" s="39" t="s">
+        <v>16</v>
+      </c>
       <c r="E23" s="3"/>
       <c r="F23" s="39" t="s">
         <v>42</v>
@@ -7502,13 +7786,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D416C393-5E79-4870-A27A-DCA7B0769528}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2A51D94-B6DC-4096-A0FB-03CB2913E5EC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3D62615-20CC-41D7-9549-DFC38910738C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{244868F9-7A85-400F-89AC-882C0C8057DC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B057C25-B0AE-4E3E-88D5-B45C14832292}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71EE0028-099C-4318-B2C0-88B597D2742C}"/>
 </file>
--- a/Plannings 2026 S41.xlsx
+++ b/Plannings 2026 S41.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E19D15AB-0DF8-4E8A-BDAD-034AB4BB581B}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B7802CF-87F2-48E9-BF75-C456FFDF9DFD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -998,8 +998,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFFFF"/>
       <color rgb="FFCCFFCC"/>
-      <color rgb="FFCCFFFF"/>
       <color rgb="FFCC99FF"/>
     </mruColors>
   </colors>
@@ -5864,7 +5864,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="B50" s="23"/>
       <c r="C50" s="23"/>
-      <c r="D50" s="23" t="s">
+      <c r="D50" s="58" t="s">
         <v>19</v>
       </c>
       <c r="E50" s="23"/>
@@ -6447,7 +6447,7 @@
       <c r="A51" s="28"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="39" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="3"/>
@@ -6461,7 +6461,7 @@
       <c r="A52" s="28"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
+      <c r="D52" s="39"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="40" t="s">
@@ -6473,7 +6473,7 @@
       <c r="A53" s="25"/>
       <c r="B53" s="26"/>
       <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
+      <c r="D53" s="41"/>
       <c r="E53" s="26"/>
       <c r="F53" s="26"/>
       <c r="G53" s="41" t="s">
@@ -7786,13 +7786,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2A51D94-B6DC-4096-A0FB-03CB2913E5EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99514D37-7E86-4B1F-AFB6-BB3F880A95BD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{244868F9-7A85-400F-89AC-882C0C8057DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715521F7-5B14-4F22-BBCE-B9016B72583B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71EE0028-099C-4318-B2C0-88B597D2742C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C99C774C-E1CE-4DF0-80FD-50E6BFF6B236}"/>
 </file>
--- a/Plannings 2026 S41.xlsx
+++ b/Plannings 2026 S41.xlsx
@@ -7786,13 +7786,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99514D37-7E86-4B1F-AFB6-BB3F880A95BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B102412-F616-441C-A40C-C25503CE20C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715521F7-5B14-4F22-BBCE-B9016B72583B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B85725B-F4BA-4404-80C2-CF4C7254870E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C99C774C-E1CE-4DF0-80FD-50E6BFF6B236}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{534881CC-617C-415D-A6F3-713E03CDA0A9}"/>
 </file>
--- a/Plannings 2026 S41.xlsx
+++ b/Plannings 2026 S41.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B7802CF-87F2-48E9-BF75-C456FFDF9DFD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,25 +17,12 @@
     <sheet name="Résultats par salarié" sheetId="2" r:id="rId2"/>
     <sheet name="Informations" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="120">
   <si>
     <t>Planning des salariés du 05/10/2026 au 11/10/2026</t>
   </si>
@@ -385,6 +372,9 @@
     <t>17:30/22:30</t>
   </si>
   <si>
+    <t>INVENTAIRE // C. PADEL // EVENT SAFRAN PU</t>
+  </si>
+  <si>
     <t>C. PADEL // EDF</t>
   </si>
   <si>
@@ -392,12 +382,6 @@
   </si>
   <si>
     <t>C. PADEL // EDF // LEAGUES</t>
-  </si>
-  <si>
-    <t>C. PADEL // EVENT GTM</t>
-  </si>
-  <si>
-    <t>09:15/11:45</t>
   </si>
 </sst>
 </file>
@@ -998,8 +982,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFFCC"/>
       <color rgb="FFCCFFFF"/>
-      <color rgb="FFCCFFCC"/>
       <color rgb="FFCC99FF"/>
     </mruColors>
   </colors>
@@ -5011,270 +4995,6 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6248400" y="8477250"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88A9096C-EADB-49D9-9206-738C26AE5526}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9593036" y="3320143"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DF5EF4D-F807-49C4-BDF3-61346F63760B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9593036" y="3701143"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ED023F5-B683-4F6E-A1C9-B3C71481A54E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9593036" y="3320143"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DC813F5-E885-4555-ABEE-3050D5FDAD78}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9593036" y="3701143"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EA533BF-E445-4206-9189-410A855FD5CF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15988393" y="3320143"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ADF761F-DA3C-4D01-9EA0-B1E0B76560BE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15988393" y="3320143"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5686,26 +5406,24 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>116</v>
-      </c>
       <c r="G3" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" s="36" t="s">
         <v>13</v>
       </c>
+      <c r="H3" s="36"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
@@ -5864,7 +5582,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
@@ -5943,8 +5661,8 @@
       <c r="C18" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="42" t="s">
-        <v>35</v>
+      <c r="D18" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="42" t="s">
@@ -5961,8 +5679,8 @@
       <c r="C19" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="43" t="s">
-        <v>120</v>
+      <c r="D19" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="43" t="s">
@@ -5977,8 +5695,8 @@
       <c r="C20" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>12</v>
+      <c r="D20" s="40" t="s">
+        <v>35</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="40" t="s">
@@ -5993,8 +5711,8 @@
       <c r="C21" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>37</v>
+      <c r="D21" s="39" t="s">
+        <v>16</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="39" t="s">
@@ -6009,9 +5727,7 @@
       <c r="C22" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="40" t="s">
-        <v>35</v>
-      </c>
+      <c r="D22" s="39"/>
       <c r="E22" s="3"/>
       <c r="F22" s="40" t="s">
         <v>35</v>
@@ -6025,9 +5741,7 @@
       <c r="C23" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="39" t="s">
-        <v>16</v>
-      </c>
+      <c r="D23" s="39"/>
       <c r="E23" s="3"/>
       <c r="F23" s="39" t="s">
         <v>42</v>
@@ -6433,7 +6147,7 @@
       </c>
       <c r="B50" s="23"/>
       <c r="C50" s="23"/>
-      <c r="D50" s="58" t="s">
+      <c r="D50" s="23" t="s">
         <v>19</v>
       </c>
       <c r="E50" s="23"/>
@@ -6447,7 +6161,7 @@
       <c r="A51" s="28"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="39" t="s">
+      <c r="D51" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="3"/>
@@ -6461,7 +6175,7 @@
       <c r="A52" s="28"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="39"/>
+      <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="40" t="s">
@@ -6473,7 +6187,7 @@
       <c r="A53" s="25"/>
       <c r="B53" s="26"/>
       <c r="C53" s="26"/>
-      <c r="D53" s="41"/>
+      <c r="D53" s="26"/>
       <c r="E53" s="26"/>
       <c r="F53" s="26"/>
       <c r="G53" s="41" t="s">
@@ -7786,13 +7500,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B102412-F616-441C-A40C-C25503CE20C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A24D7A2B-9FD9-411E-9456-3A78290D458E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B85725B-F4BA-4404-80C2-CF4C7254870E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFCF5860-6BE1-4684-838A-E84D137BACE4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{534881CC-617C-415D-A6F3-713E03CDA0A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{880A5CE2-4B9F-4A75-A43E-CA6BA6DAC4DB}"/>
 </file>
--- a/Plannings 2026 S41.xlsx
+++ b/Plannings 2026 S41.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B7802CF-87F2-48E9-BF75-C456FFDF9DFD}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{37694237-19EA-44DF-ACA0-E2985A841EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8593F449-8315-426C-9F04-1A01528B2E77}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="122">
   <si>
     <t>Planning des salariés du 05/10/2026 au 11/10/2026</t>
   </si>
@@ -398,6 +398,9 @@
   </si>
   <si>
     <t>09:15/11:45</t>
+  </si>
+  <si>
+    <t>C. PADEL // P25 // EDF // LEAGUES</t>
   </si>
 </sst>
 </file>
@@ -5686,7 +5689,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="36" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C3" s="36" t="s">
         <v>118</v>
@@ -7786,13 +7789,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B102412-F616-441C-A40C-C25503CE20C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD5FF5C2-7BDD-4AD6-9F7E-2B87B6F8F1E2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B85725B-F4BA-4404-80C2-CF4C7254870E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53B7F5AF-8906-4EDE-85FB-358033063565}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{534881CC-617C-415D-A6F3-713E03CDA0A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19E42DB0-6EB2-4E5D-8EA5-4644AC49440D}"/>
 </file>